--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_BRK-CSTD-2-00-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_BRK-CSTD-2-00-A-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\s10035azcfs0534.file.core.windows.net\metersoft\開発用\Toyota\BEV\kse\_仮置き\02.設計\07.MET-C_BRK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\s10035azcfs0534.file.core.windows.net\metersoft\開発用\Toyota\BEV\設計成果物_MET\MCU-DT\02設計\01.シス検\MET-C_BRK_CSTD_BEV3CDCMET-38\04.パラメータ設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6587216-0DF9-4AD1-A5A8-C99CF317D923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBBE082-13A0-4DFE-BA25-32B96981CC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="620" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" tabRatio="620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -529,7 +529,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2501" uniqueCount="297">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2861,6 +2861,70 @@
 C_BRK-CSTD-2-MEF01-REQ02-</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>BEV シス検#1対応
+[Matrix]シート
+・対象仕様書変更
+・ロケーション変更
+[CH_Design]シート
+・CH名、要求IDを仕様Verに合わせて変更
+[C_BRK_2]シート
+・仕様変更に合わせて変更
+[Reference]シート
+・各キャプチャ画像を変更</t>
+    <rPh sb="6" eb="7">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ヨウキュウ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="97" eb="99">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>5.4.0</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>KSE深町日響</t>
+    <rPh sb="3" eb="7">
+      <t>フカマチヒヒビキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1.1.0</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -5016,7 +5080,14 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5028,13 +5099,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5074,28 +5138,8 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -10271,7 +10315,7 @@
       <c r="D4" s="6"/>
       <c r="E4" s="22" t="str">
         <f>DGET(B8:C15,"Ver.",H4:H5)</f>
-        <v>1.0.0</v>
+        <v>1.1.0</v>
       </c>
       <c r="F4" s="6"/>
       <c r="H4" s="9" t="s">
@@ -10285,7 +10329,7 @@
       <c r="F5" s="6"/>
       <c r="H5" s="11">
         <f>MAX(B9:B15)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="14.25" thickBot="1"/>
@@ -10414,27 +10458,59 @@
         <v>44278</v>
       </c>
     </row>
-    <row r="10" spans="2:18">
+    <row r="10" spans="2:18" ht="135">
       <c r="B10" s="9">
         <f>IF(C10=0,0,ROW()-ROW($B$8))</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="200"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="186"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="186"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="180"/>
+        <v>2</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="D10" s="200" t="s">
+        <v>293</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="L10" s="186">
+        <v>45637</v>
+      </c>
+      <c r="M10" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="O10" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q10" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="R10" s="180" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="11" spans="2:18">
       <c r="B11" s="9">
@@ -11914,24 +11990,19 @@
     <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="C14:C37">
-    <cfRule type="expression" dxfId="10" priority="5">
-      <formula>14&lt;LEN($D$6)+LEN($C14)</formula>
+  <conditionalFormatting sqref="C13:C37">
+    <cfRule type="expression" dxfId="8" priority="1">
+      <formula>14&lt;LEN($D$6)+LEN($C13)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="NG">
+      <formula>NOT(ISERROR(SEARCH("NG",D5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="9" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>14 &lt; LEN($D$6)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5">
-    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="NG">
-      <formula>NOT(ISERROR(SEARCH("NG",D5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="7" priority="1">
-      <formula>14&lt;LEN($D$6)+LEN($C13)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -15960,12 +16031,7 @@
     <protectedRange sqref="B4:L9" name="範囲1_3"/>
   </protectedRanges>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="M4:M102">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
-      <formula>32</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3">
+  <conditionalFormatting sqref="M3:M102">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
       <formula>32</formula>
     </cfRule>
@@ -44882,17 +44948,17 @@
       <formula>"×"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AR5:AS70">
-    <cfRule type="expression" dxfId="2" priority="7">
-      <formula>$B$3="Index Table"</formula>
+  <conditionalFormatting sqref="AC37">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"×"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC37">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"×"</formula>
+  <conditionalFormatting sqref="AR5:AS70">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>$B$3="Index Table"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
